--- a/Excel/AttrEntryConfig.xlsx
+++ b/Excel/AttrEntryConfig.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WrittenLegend\Excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="2"/>
+    <workbookView windowHeight="17680" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="普通装备" sheetId="1" r:id="rId1"/>
@@ -128,7 +133,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="430" uniqueCount="78">
   <si>
     <t>_ID</t>
   </si>
@@ -293,6 +298,18 @@
   </si>
   <si>
     <t>破韧倍率</t>
+  </si>
+  <si>
+    <t>61,63</t>
+  </si>
+  <si>
+    <t>69,70</t>
+  </si>
+  <si>
+    <t>61,62,63,64,65,67,69,70</t>
+  </si>
+  <si>
+    <t>62,64,65,69,70</t>
   </si>
   <si>
     <t>神话攻击</t>
@@ -528,12 +545,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -3312,7 +3329,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:L76"/>
+  <dimension ref="C3:L92"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
@@ -5568,6 +5585,486 @@
         <v>2</v>
       </c>
       <c r="L76" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="3:12">
+      <c r="C78" s="1">
+        <v>73</v>
+      </c>
+      <c r="D78" s="1">
+        <v>7</v>
+      </c>
+      <c r="E78" s="1">
+        <v>1</v>
+      </c>
+      <c r="F78" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G78" s="1">
+        <v>400</v>
+      </c>
+      <c r="H78" s="1">
+        <v>800</v>
+      </c>
+      <c r="I78" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="J78" s="1">
+        <v>7</v>
+      </c>
+      <c r="K78" s="1">
+        <v>6</v>
+      </c>
+      <c r="L78" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="3:12">
+      <c r="C79" s="1">
+        <v>74</v>
+      </c>
+      <c r="D79" s="1">
+        <v>55</v>
+      </c>
+      <c r="E79" s="1">
+        <v>1</v>
+      </c>
+      <c r="F79" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G79" s="1">
+        <v>2</v>
+      </c>
+      <c r="H79" s="1">
+        <v>4</v>
+      </c>
+      <c r="I79" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="J79" s="1">
+        <v>7</v>
+      </c>
+      <c r="K79" s="1">
+        <v>2</v>
+      </c>
+      <c r="L79" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="3:12">
+      <c r="C80" s="1">
+        <v>75</v>
+      </c>
+      <c r="D80" s="1">
+        <v>54</v>
+      </c>
+      <c r="E80" s="1">
+        <v>1</v>
+      </c>
+      <c r="F80" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G80" s="1">
+        <v>2</v>
+      </c>
+      <c r="H80" s="1">
+        <v>4</v>
+      </c>
+      <c r="I80" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="J80" s="1">
+        <v>7</v>
+      </c>
+      <c r="K80" s="1">
+        <v>2</v>
+      </c>
+      <c r="L80" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="3:12">
+      <c r="C81" s="1">
+        <v>76</v>
+      </c>
+      <c r="D81" s="1">
+        <v>2004</v>
+      </c>
+      <c r="E81" s="1">
+        <v>1</v>
+      </c>
+      <c r="F81" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G81" s="1">
+        <v>25</v>
+      </c>
+      <c r="H81" s="1">
+        <v>60</v>
+      </c>
+      <c r="I81" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="J81" s="1">
+        <v>7</v>
+      </c>
+      <c r="K81" s="3">
+        <v>3</v>
+      </c>
+      <c r="L81" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82" spans="3:12">
+      <c r="C82" s="1">
+        <v>77</v>
+      </c>
+      <c r="D82" s="1">
+        <v>2005</v>
+      </c>
+      <c r="E82" s="1">
+        <v>1</v>
+      </c>
+      <c r="F82" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G82" s="1">
+        <v>25</v>
+      </c>
+      <c r="H82" s="1">
+        <v>60</v>
+      </c>
+      <c r="I82" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="J82" s="1">
+        <v>7</v>
+      </c>
+      <c r="K82" s="3">
+        <v>3</v>
+      </c>
+      <c r="L82" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="83" spans="3:12">
+      <c r="C83" s="1">
+        <v>78</v>
+      </c>
+      <c r="D83" s="1">
+        <v>2006</v>
+      </c>
+      <c r="E83" s="1">
+        <v>1</v>
+      </c>
+      <c r="F83" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G83" s="1">
+        <v>25</v>
+      </c>
+      <c r="H83" s="1">
+        <v>60</v>
+      </c>
+      <c r="I83" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="J83" s="1">
+        <v>7</v>
+      </c>
+      <c r="K83" s="3">
+        <v>3</v>
+      </c>
+      <c r="L83" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:12">
+      <c r="C84" s="1">
+        <v>79</v>
+      </c>
+      <c r="D84" s="1">
+        <v>33</v>
+      </c>
+      <c r="E84" s="1">
+        <v>1</v>
+      </c>
+      <c r="F84" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G84" s="1">
+        <v>400</v>
+      </c>
+      <c r="H84" s="1">
+        <v>800</v>
+      </c>
+      <c r="I84" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="J84" s="1">
+        <v>7</v>
+      </c>
+      <c r="K84" s="3">
+        <v>6</v>
+      </c>
+      <c r="L84" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85" spans="3:12">
+      <c r="C85" s="1">
+        <v>80</v>
+      </c>
+      <c r="D85" s="1">
+        <v>34</v>
+      </c>
+      <c r="E85" s="1">
+        <v>1</v>
+      </c>
+      <c r="F85" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G85" s="1">
+        <v>400</v>
+      </c>
+      <c r="H85" s="1">
+        <v>800</v>
+      </c>
+      <c r="I85" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="J85" s="1">
+        <v>7</v>
+      </c>
+      <c r="K85" s="3">
+        <v>6</v>
+      </c>
+      <c r="L85" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="86" spans="3:12">
+      <c r="C86" s="1">
+        <v>81</v>
+      </c>
+      <c r="D86" s="1">
+        <v>35</v>
+      </c>
+      <c r="E86" s="1">
+        <v>1</v>
+      </c>
+      <c r="F86" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G86" s="1">
+        <v>400</v>
+      </c>
+      <c r="H86" s="1">
+        <v>800</v>
+      </c>
+      <c r="I86" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="J86" s="1">
+        <v>7</v>
+      </c>
+      <c r="K86" s="3">
+        <v>6</v>
+      </c>
+      <c r="L86" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="87" spans="3:12">
+      <c r="C87" s="1">
+        <v>82</v>
+      </c>
+      <c r="D87" s="1">
+        <v>2001</v>
+      </c>
+      <c r="E87" s="1">
+        <v>1</v>
+      </c>
+      <c r="F87" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="G87" s="1">
+        <v>25</v>
+      </c>
+      <c r="H87" s="1">
+        <v>60</v>
+      </c>
+      <c r="I87" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="J87" s="1">
+        <v>7</v>
+      </c>
+      <c r="K87" s="3">
+        <v>2</v>
+      </c>
+      <c r="L87" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:12">
+      <c r="C88" s="1">
+        <v>83</v>
+      </c>
+      <c r="D88" s="1">
+        <v>2002</v>
+      </c>
+      <c r="E88" s="1">
+        <v>1</v>
+      </c>
+      <c r="F88" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G88" s="1">
+        <v>25</v>
+      </c>
+      <c r="H88" s="1">
+        <v>60</v>
+      </c>
+      <c r="I88" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="J88" s="1">
+        <v>7</v>
+      </c>
+      <c r="K88" s="3">
+        <v>5</v>
+      </c>
+      <c r="L88" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:12">
+      <c r="C89" s="1">
+        <v>84</v>
+      </c>
+      <c r="D89" s="1">
+        <v>2003</v>
+      </c>
+      <c r="E89" s="1">
+        <v>1</v>
+      </c>
+      <c r="F89" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G89" s="1">
+        <v>25</v>
+      </c>
+      <c r="H89" s="1">
+        <v>60</v>
+      </c>
+      <c r="I89" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="J89" s="1">
+        <v>7</v>
+      </c>
+      <c r="K89" s="3">
+        <v>5</v>
+      </c>
+      <c r="L89" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:12">
+      <c r="C90" s="1">
+        <v>85</v>
+      </c>
+      <c r="D90" s="1">
+        <v>2012</v>
+      </c>
+      <c r="E90" s="1">
+        <v>1</v>
+      </c>
+      <c r="F90" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G90" s="1">
+        <v>25</v>
+      </c>
+      <c r="H90" s="1">
+        <v>60</v>
+      </c>
+      <c r="I90" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="J90" s="1">
+        <v>7</v>
+      </c>
+      <c r="K90" s="3">
+        <v>5</v>
+      </c>
+      <c r="L90" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="3:12">
+      <c r="C91" s="1">
+        <v>86</v>
+      </c>
+      <c r="D91" s="1">
+        <v>2010</v>
+      </c>
+      <c r="E91" s="1">
+        <v>1</v>
+      </c>
+      <c r="F91" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G91" s="1">
+        <v>25</v>
+      </c>
+      <c r="H91" s="1">
+        <v>60</v>
+      </c>
+      <c r="I91" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="J91" s="1">
+        <v>7</v>
+      </c>
+      <c r="K91" s="3">
+        <v>2</v>
+      </c>
+      <c r="L91" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:12">
+      <c r="C92" s="1">
+        <v>87</v>
+      </c>
+      <c r="D92" s="1">
+        <v>2013</v>
+      </c>
+      <c r="E92" s="1">
+        <v>1</v>
+      </c>
+      <c r="F92" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="G92" s="1">
+        <v>25</v>
+      </c>
+      <c r="H92" s="1">
+        <v>60</v>
+      </c>
+      <c r="I92" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="J92" s="1">
+        <v>7</v>
+      </c>
+      <c r="K92" s="3">
+        <v>2</v>
+      </c>
+      <c r="L92" s="1">
         <v>0</v>
       </c>
     </row>
@@ -5707,7 +6204,7 @@
         <v>6</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="G6" s="1">
         <v>1</v>
@@ -5716,7 +6213,7 @@
         <v>10</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="J6" s="1">
         <v>99</v>
@@ -5739,7 +6236,7 @@
         <v>6</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="G7" s="1">
         <v>1</v>
@@ -5748,7 +6245,7 @@
         <v>10</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="J7" s="1">
         <v>99</v>
@@ -5771,7 +6268,7 @@
         <v>6</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="G8" s="1">
         <v>1</v>
@@ -5780,7 +6277,7 @@
         <v>10</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="J8" s="1">
         <v>99</v>
@@ -5812,7 +6309,7 @@
         <v>100</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="J9" s="1">
         <v>99</v>
@@ -5844,7 +6341,7 @@
         <v>100</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="J10" s="1">
         <v>99</v>
@@ -5867,7 +6364,7 @@
         <v>7</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="G11" s="1">
         <v>25</v>
@@ -5876,7 +6373,7 @@
         <v>100</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="J11" s="1">
         <v>99</v>
@@ -5899,7 +6396,7 @@
         <v>8</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="G12" s="1">
         <v>25</v>
@@ -5908,7 +6405,7 @@
         <v>100</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="J12" s="1">
         <v>99</v>
@@ -5931,7 +6428,7 @@
         <v>8</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="G13" s="1">
         <v>25</v>
@@ -5940,7 +6437,7 @@
         <v>100</v>
       </c>
       <c r="I13" s="4" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="J13" s="1">
         <v>99</v>
@@ -5963,7 +6460,7 @@
         <v>8</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="G14" s="1">
         <v>25</v>
@@ -5972,7 +6469,7 @@
         <v>100</v>
       </c>
       <c r="I14" s="4" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="J14" s="1">
         <v>99</v>
@@ -6004,7 +6501,7 @@
         <v>100</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="J15" s="1">
         <v>99</v>
@@ -6030,7 +6527,7 @@
         <v>6</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="G17" s="1">
         <v>1</v>
@@ -6039,7 +6536,7 @@
         <v>13</v>
       </c>
       <c r="I17" s="4" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="J17" s="1">
         <v>99</v>
@@ -6062,7 +6559,7 @@
         <v>6</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="G18" s="1">
         <v>1</v>
@@ -6071,7 +6568,7 @@
         <v>13</v>
       </c>
       <c r="I18" s="4" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="J18" s="1">
         <v>99</v>
@@ -6094,7 +6591,7 @@
         <v>6</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="G19" s="1">
         <v>1</v>
@@ -6103,7 +6600,7 @@
         <v>13</v>
       </c>
       <c r="I19" s="4" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="J19" s="1">
         <v>99</v>
@@ -6135,7 +6632,7 @@
         <v>200</v>
       </c>
       <c r="I20" s="4" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="J20" s="1">
         <v>99</v>
@@ -6167,7 +6664,7 @@
         <v>200</v>
       </c>
       <c r="I21" s="4" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="J21" s="1">
         <v>99</v>
@@ -6190,7 +6687,7 @@
         <v>7</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="G22" s="1">
         <v>25</v>
@@ -6199,7 +6696,7 @@
         <v>200</v>
       </c>
       <c r="I22" s="4" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="J22" s="1">
         <v>99</v>
@@ -6222,7 +6719,7 @@
         <v>8</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="G23" s="1">
         <v>25</v>
@@ -6231,7 +6728,7 @@
         <v>200</v>
       </c>
       <c r="I23" s="4" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="J23" s="1">
         <v>99</v>
@@ -6254,7 +6751,7 @@
         <v>8</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="G24" s="1">
         <v>25</v>
@@ -6263,7 +6760,7 @@
         <v>200</v>
       </c>
       <c r="I24" s="4" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="J24" s="1">
         <v>99</v>
@@ -6286,7 +6783,7 @@
         <v>8</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="G25" s="1">
         <v>25</v>
@@ -6295,7 +6792,7 @@
         <v>200</v>
       </c>
       <c r="I25" s="4" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="J25" s="1">
         <v>99</v>
@@ -6327,7 +6824,7 @@
         <v>200</v>
       </c>
       <c r="I26" s="4" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="J26" s="1">
         <v>99</v>
@@ -6350,7 +6847,7 @@
         <v>6</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="G29" s="1">
         <v>1</v>
@@ -6359,7 +6856,7 @@
         <v>18</v>
       </c>
       <c r="I29" s="4" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="J29" s="1">
         <v>99</v>
@@ -6382,7 +6879,7 @@
         <v>6</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="G30" s="1">
         <v>1</v>
@@ -6391,7 +6888,7 @@
         <v>18</v>
       </c>
       <c r="I30" s="4" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="J30" s="1">
         <v>99</v>
@@ -6414,7 +6911,7 @@
         <v>6</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="G31" s="1">
         <v>1</v>
@@ -6423,7 +6920,7 @@
         <v>18</v>
       </c>
       <c r="I31" s="4" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="J31" s="1">
         <v>99</v>
@@ -6455,7 +6952,7 @@
         <v>250</v>
       </c>
       <c r="I32" s="4" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="J32" s="1">
         <v>99</v>
@@ -6487,7 +6984,7 @@
         <v>250</v>
       </c>
       <c r="I33" s="4" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="J33" s="1">
         <v>99</v>
@@ -6510,7 +7007,7 @@
         <v>7</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="G34" s="1">
         <v>25</v>
@@ -6519,7 +7016,7 @@
         <v>250</v>
       </c>
       <c r="I34" s="4" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="J34" s="1">
         <v>99</v>
@@ -6542,7 +7039,7 @@
         <v>8</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="G35" s="1">
         <v>25</v>
@@ -6551,7 +7048,7 @@
         <v>250</v>
       </c>
       <c r="I35" s="4" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="J35" s="1">
         <v>99</v>
@@ -6574,7 +7071,7 @@
         <v>8</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="G36" s="1">
         <v>25</v>
@@ -6583,7 +7080,7 @@
         <v>250</v>
       </c>
       <c r="I36" s="4" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="J36" s="1">
         <v>99</v>
@@ -6606,7 +7103,7 @@
         <v>8</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="G37" s="1">
         <v>25</v>
@@ -6615,7 +7112,7 @@
         <v>250</v>
       </c>
       <c r="I37" s="4" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="J37" s="1">
         <v>99</v>
@@ -6647,7 +7144,7 @@
         <v>250</v>
       </c>
       <c r="I38" s="4" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="J38" s="1">
         <v>99</v>
